--- a/r5-aist-trustworthyai-main/ValueSet-gdpr-art6-legal-basis-vs.xlsx
+++ b/r5-aist-trustworthyai-main/ValueSet-gdpr-art6-legal-basis-vs.xlsx
@@ -42,13 +42,13 @@
     <t>Title</t>
   </si>
   <si>
-    <t>GDPR Art 6 Legal Basis for AI</t>
+    <t>GDPR Article 6 Legal Basis ValueSet</t>
   </si>
   <si>
     <t>Status</t>
   </si>
   <si>
-    <t>draft</t>
+    <t>active</t>
   </si>
   <si>
     <t>Experimental</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T08:40:47+00:00</t>
+    <t>2026-06-18T12:04:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-aist-trustworthyai-main/ValueSet-gdpr-art6-legal-basis-vs.xlsx
+++ b/r5-aist-trustworthyai-main/ValueSet-gdpr-art6-legal-basis-vs.xlsx
@@ -36,13 +36,13 @@
     <t>Name</t>
   </si>
   <si>
-    <t>GDPR_Art6_LegalBasisVS</t>
+    <t>GDPRArt6LegalBasisVS</t>
   </si>
   <si>
     <t>Title</t>
   </si>
   <si>
-    <t>GDPR Article 6 Legal Basis ValueSet</t>
+    <t>GDPR Article 6 Legal Basis Value Set</t>
   </si>
   <si>
     <t>Status</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T12:04:51+00:00</t>
+    <t>2026-07-31T11:07:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -78,7 +78,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Value set including GDPR Article 6 legal bases relevant for documenting the lawful processing of personal data.</t>
+    <t>Legal bases listed in Article 6(1) GDPR for documenting the asserted lawful basis for processing personal data.</t>
   </si>
   <si>
     <t>Purpose</t>

--- a/r5-aist-trustworthyai-main/ValueSet-gdpr-art6-legal-basis-vs.xlsx
+++ b/r5-aist-trustworthyai-main/ValueSet-gdpr-art6-legal-basis-vs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-31T11:07:29+00:00</t>
+    <t>2026-09-02T10:48:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-aist-trustworthyai-main/ValueSet-gdpr-art6-legal-basis-vs.xlsx
+++ b/r5-aist-trustworthyai-main/ValueSet-gdpr-art6-legal-basis-vs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T10:48:14+00:00</t>
+    <t>2026-09-03T11:53:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-aist-trustworthyai-main/ValueSet-gdpr-art6-legal-basis-vs.xlsx
+++ b/r5-aist-trustworthyai-main/ValueSet-gdpr-art6-legal-basis-vs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-03T11:53:05+00:00</t>
+    <t>2026-09-07T08:39:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-aist-trustworthyai-main/ValueSet-gdpr-art6-legal-basis-vs.xlsx
+++ b/r5-aist-trustworthyai-main/ValueSet-gdpr-art6-legal-basis-vs.xlsx
@@ -24,7 +24,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>http://example.org/fhir/eu-ai-transparency/ValueSet/gdpr-art6-legal-basis-vs</t>
+    <t>http://example.org/fhir/trust-ai-transparency/ValueSet/gdpr-art6-legal-basis-vs</t>
   </si>
   <si>
     <t>Version</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-07T08:39:53+00:00</t>
+    <t>2026-09-09T11:13:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -102,7 +102,7 @@
     <t>System URI</t>
   </si>
   <si>
-    <t>http://example.org/fhir/eu-ai-transparency/CodeSystem/gdpr-art6-codesystem</t>
+    <t>http://example.org/fhir/trust-ai-transparency/CodeSystem/gdpr-art6-codesystem</t>
   </si>
 </sst>
 </file>
